--- a/naver-place-crawler/results_health/청주_헬스장.xlsx
+++ b/naver-place-crawler/results_health/청주_헬스장.xlsx
@@ -421,8 +421,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="25" customWidth="1" min="2" max="2"/>
-    <col width="27" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
@@ -564,29 +564,29 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>휘트니스휴 동남지구점</t>
+          <t>24시 코코피트니스 헬스PT태닝 프리미엄 강서점</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>fithue9679@naver.com</t>
+          <t>grasp1069@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1357-9680</t>
+          <t>0507-1336-5246</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>충북 청주시 상당구 호미로 3 4층</t>
+          <t>충북 청주시 흥덕구 강서로 110 3층</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/fithue9679</t>
+          <t>https://blog.naver.com/grasp1069</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -611,7 +611,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4547b</t>
+          <t>https://talk.naver.com/ct/w4d0wj</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -625,13 +625,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>871</v>
+        <v>4752</v>
       </c>
       <c r="Q2" t="n">
-        <v>618</v>
+        <v>1281</v>
       </c>
       <c r="R2" t="n">
-        <v>1489</v>
+        <v>6033</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -640,17 +640,17 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1870900978</t>
+          <t>1446407109</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1870900978</t>
+          <t>https://m.place.naver.com/place/1446407109</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -662,29 +662,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>24시 코코피트니스 헬스PT필라테스 산남점</t>
+          <t>휘트니스휴 동남지구점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>cocogym1@naver.com</t>
+          <t>fithue9679@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1354-0050</t>
+          <t>0507-1357-9680</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>충북 청주시 서원구 원흥로 17 3층</t>
+          <t>충북 청주시 상당구 호미로 3 4층</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/cocogym1</t>
+          <t>https://blog.naver.com/fithue9679</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -709,7 +709,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4otcd</t>
+          <t>https://talk.naver.com/ct/w4547b</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -723,13 +723,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>3758</v>
+        <v>874</v>
       </c>
       <c r="Q3" t="n">
-        <v>2059</v>
+        <v>618</v>
       </c>
       <c r="R3" t="n">
-        <v>5817</v>
+        <v>1492</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -738,17 +738,17 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1286616507</t>
+          <t>1870900978</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1286616507</t>
+          <t>https://m.place.naver.com/place/1870900978</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -760,29 +760,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>코코피트니스 헬스 PT 태닝 복대점</t>
+          <t>24시 코코피트니스 헬스PT필라테스 산남점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>cocogym_3@naver.com</t>
+          <t>cocogym1@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1443-0339</t>
+          <t>0507-1354-0050</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>충북 청주시 흥덕구 대농로 43 4층</t>
+          <t>충북 청주시 서원구 원흥로 17 3층</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/@cocogym3</t>
+          <t>https://blog.naver.com/cocogym1</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -797,7 +797,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -807,7 +807,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4ammk</t>
+          <t>https://talk.naver.com/ct/w4otcd</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -821,13 +821,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>3058</v>
+        <v>3758</v>
       </c>
       <c r="Q4" t="n">
-        <v>1810</v>
+        <v>2064</v>
       </c>
       <c r="R4" t="n">
-        <v>4868</v>
+        <v>5822</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -836,17 +836,17 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1478272953</t>
+          <t>1286616507</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1478272953</t>
+          <t>https://m.place.naver.com/place/1286616507</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -858,29 +858,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>24시 코코피트니스 헬스 PT 율량점</t>
+          <t>코코피트니스 헬스 PT 태닝 복대점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>shaminwoo@naver.com</t>
+          <t>cocogym_3@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1377-5496</t>
+          <t>0507-1443-0339</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>충북 청주시 청원구 율량로190번길 53 비 제4층 제404호</t>
+          <t>충북 청주시 흥덕구 대농로 43 4층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/coco_fitxx8</t>
+          <t>https://www.youtube.com/@cocogym3</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -905,7 +905,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wy2mfy3</t>
+          <t>https://talk.naver.com/ct/w4ammk</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -919,13 +919,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>274</v>
+        <v>3064</v>
       </c>
       <c r="Q5" t="n">
-        <v>334</v>
+        <v>1811</v>
       </c>
       <c r="R5" t="n">
-        <v>608</v>
+        <v>4875</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -934,17 +934,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2051104888</t>
+          <t>1478272953</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2051104888</t>
+          <t>https://m.place.naver.com/place/1478272953</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1017,13 +1017,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>2656</v>
+        <v>2660</v>
       </c>
       <c r="Q6" t="n">
-        <v>1527</v>
+        <v>1533</v>
       </c>
       <c r="R6" t="n">
-        <v>4183</v>
+        <v>4193</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1042,41 +1042,41 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>브로피트니스 금천점 PT헬스</t>
+          <t>24시 코코피트니스 헬스 PT 율량점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>brofitness2@naver.com</t>
+          <t>shaminwoo@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1342-9698</t>
+          <t>0507-1377-5496</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>충북 청주시 상당구 중고개로 307 4층</t>
+          <t>충북 청주시 청원구 율량로190번길 53 비 제4층 제404호</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/brofitness2</t>
+          <t>https://www.instagram.com/coco_fitxx8</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4d52a</t>
+          <t>https://talk.naver.com/ct/wy2mfy3</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1115,13 +1115,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>614</v>
+        <v>282</v>
       </c>
       <c r="Q7" t="n">
-        <v>813</v>
+        <v>341</v>
       </c>
       <c r="R7" t="n">
-        <v>1427</v>
+        <v>623</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1130,55 +1130,51 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1563089367</t>
+          <t>2051104888</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1563089367</t>
+          <t>https://m.place.naver.com/place/2051104888</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>쿠키짐 헬스&amp;PT 오송</t>
+          <t>브로피트니스 금천점 PT헬스</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>cookiegym@naver.com</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>gotz6170@gmail.com</t>
-        </is>
-      </c>
+          <t>brofitness2@naver.com</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1371-9224</t>
+          <t>0507-1342-9698</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>충북 청주시 흥덕구 오송읍 오송생명11로 46 608~621호</t>
+          <t>충북 청주시 상당구 중고개로 307 4층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://youtu.be/UXuiUC4s92M?si=R4exOLNx-6qFB1fg</t>
+          <t>https://blog.naver.com/brofitness2</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1193,7 +1189,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1203,7 +1199,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4h6q3</t>
+          <t>https://talk.naver.com/ct/w4d52a</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1217,13 +1213,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>3354</v>
+        <v>614</v>
       </c>
       <c r="Q8" t="n">
-        <v>840</v>
+        <v>823</v>
       </c>
       <c r="R8" t="n">
-        <v>4194</v>
+        <v>1437</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1232,17 +1228,17 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1245970521</t>
+          <t>1563089367</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1245970521</t>
+          <t>https://m.place.naver.com/place/1563089367</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1254,29 +1250,33 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>네오바디짐 율량점 헬스 PT</t>
+          <t>쿠키짐 헬스&amp;PT 오송</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>neobodygym@naver.com</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>cookiegym@naver.com</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>gotz6170@gmail.com</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1314-5116</t>
+          <t>0507-1371-9224</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>충북 청주시 청원구 사뜸로 70 상가동 지하1층</t>
+          <t>충북 청주시 흥덕구 오송읍 오송생명11로 46 608~621호</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/neobodygym</t>
+          <t>https://youtu.be/UXuiUC4s92M?si=R4exOLNx-6qFB1fg</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wy4h5jc</t>
+          <t>https://talk.naver.com/ct/w4h6q3</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1315,13 +1315,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>114</v>
+        <v>3355</v>
       </c>
       <c r="Q9" t="n">
-        <v>59</v>
+        <v>850</v>
       </c>
       <c r="R9" t="n">
-        <v>173</v>
+        <v>4205</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1330,51 +1330,51 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2045981331</t>
+          <t>1245970521</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2045981331</t>
+          <t>https://m.place.naver.com/place/1245970521</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>빅스짐 청주고속터미널점</t>
+          <t>팀온짐 강서점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>bigsgymgagyeong@naver.com</t>
+          <t>wkddlfwns13@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1364-8896</t>
+          <t>0507-1394-8311</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>충북 청주시 흥덕구 강서로 118 장한빌딩 6층 601-605호</t>
+          <t>충북 청주시 흥덕구 가로수로1164번길 41-29 4층 팀온짐</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/bigsgym_cheongju/</t>
+          <t>https://www.instagram.com/team.on.gym_gangseo/</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1399,7 +1399,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w456me</t>
+          <t>https://talk.naver.com/ct/w42g0e</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1413,13 +1413,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>5288</v>
+        <v>99</v>
       </c>
       <c r="Q10" t="n">
-        <v>1287</v>
+        <v>54</v>
       </c>
       <c r="R10" t="n">
-        <v>6575</v>
+        <v>153</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1428,17 +1428,17 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1689856448</t>
+          <t>1332607968</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1689856448</t>
+          <t>https://m.place.naver.com/place/1332607968</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1510,10 +1510,10 @@
         <v>283</v>
       </c>
       <c r="Q11" t="n">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="R11" t="n">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/청주_헬스장.xlsx
+++ b/naver-place-crawler/results_health/청주_헬스장.xlsx
@@ -423,7 +423,7 @@
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="28" customWidth="1" min="2" max="2"/>
     <col width="27" customWidth="1" min="3" max="3"/>
-    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="41" customWidth="1" min="7" max="7"/>
@@ -625,13 +625,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>4760</v>
+        <v>4766</v>
       </c>
       <c r="Q2" t="n">
-        <v>1282</v>
+        <v>1283</v>
       </c>
       <c r="R2" t="n">
-        <v>6042</v>
+        <v>6049</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -824,10 +824,10 @@
         <v>3758</v>
       </c>
       <c r="Q4" t="n">
-        <v>2065</v>
+        <v>2067</v>
       </c>
       <c r="R4" t="n">
-        <v>5823</v>
+        <v>5825</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -922,10 +922,10 @@
         <v>3064</v>
       </c>
       <c r="Q5" t="n">
-        <v>1812</v>
+        <v>1814</v>
       </c>
       <c r="R5" t="n">
-        <v>4876</v>
+        <v>4878</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -1017,13 +1017,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q6" t="n">
         <v>340</v>
       </c>
       <c r="R6" t="n">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1115,13 +1115,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>2662</v>
+        <v>2667</v>
       </c>
       <c r="Q7" t="n">
         <v>1534</v>
       </c>
       <c r="R7" t="n">
-        <v>4196</v>
+        <v>4201</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1318,10 +1318,10 @@
         <v>614</v>
       </c>
       <c r="Q9" t="n">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="R9" t="n">
-        <v>1438</v>
+        <v>1439</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1445,38 +1445,34 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>짐타이밍</t>
+          <t>PT라운지 복대점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>gymtiming1@naver.com</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>jayoufree@gmail.com</t>
-        </is>
-      </c>
+          <t>pt_lounge@naver.com</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>043-297-0220</t>
+          <t>0507-1408-0133</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>충북 청주시 서원구 산남로70번길 34 7층</t>
+          <t>충북 청주시 흥덕구 대농로 68 MJ트윈스빌딩 601호 PT라운지</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://youtube.com/@짐타이밍QED골프/shorts</t>
+          <t>https://blog.naver.com/pt_lounge</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1491,7 +1487,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1501,7 +1497,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4dqvo</t>
+          <t>https://talk.naver.com/ct/w4xfjq</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1515,13 +1511,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>326</v>
+        <v>449</v>
       </c>
       <c r="Q11" t="n">
-        <v>442</v>
+        <v>955</v>
       </c>
       <c r="R11" t="n">
-        <v>768</v>
+        <v>1404</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1530,12 +1526,12 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>13145981</t>
+          <t>1945520016</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13145981</t>
+          <t>https://m.place.naver.com/place/1945520016</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">

--- a/naver-place-crawler/results_health/청주_헬스장.xlsx
+++ b/naver-place-crawler/results_health/청주_헬스장.xlsx
@@ -417,11 +417,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V12"/>
+  <dimension ref="A1:V11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
     <col width="27" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
@@ -564,29 +564,29 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>24시 코코피트니스 헬스PT태닝 프리미엄 강서점</t>
+          <t>휘트니스휴 동남지구점</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>grasp1069@naver.com</t>
+          <t>fithue9679@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1336-5246</t>
+          <t>0507-1357-9680</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>충북 청주시 흥덕구 강서로 110 3층</t>
+          <t>충북 청주시 상당구 호미로 3 4층</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/grasp1069</t>
+          <t>https://blog.naver.com/fithue9679</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -611,7 +611,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4d0wj</t>
+          <t>https://talk.naver.com/ct/w4547b</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -625,13 +625,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>4766</v>
+        <v>876</v>
       </c>
       <c r="Q2" t="n">
-        <v>1283</v>
+        <v>618</v>
       </c>
       <c r="R2" t="n">
-        <v>6049</v>
+        <v>1494</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -640,17 +640,17 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1446407109</t>
+          <t>1870900978</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1446407109</t>
+          <t>https://m.place.naver.com/place/1870900978</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -662,29 +662,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>휘트니스휴 동남지구점</t>
+          <t>24시 코코피트니스 헬스PT필라테스 산남점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>fithue9679@naver.com</t>
+          <t>cocogym1@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1357-9680</t>
+          <t>0507-1354-0050</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>충북 청주시 상당구 호미로 3 4층</t>
+          <t>충북 청주시 서원구 원흥로 17 3층</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/fithue9679</t>
+          <t>https://blog.naver.com/cocogym1</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -709,7 +709,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4547b</t>
+          <t>https://talk.naver.com/ct/w4otcd</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -723,13 +723,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>876</v>
+        <v>3758</v>
       </c>
       <c r="Q3" t="n">
-        <v>618</v>
+        <v>2067</v>
       </c>
       <c r="R3" t="n">
-        <v>1494</v>
+        <v>5825</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -738,17 +738,17 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1870900978</t>
+          <t>1286616507</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1870900978</t>
+          <t>https://m.place.naver.com/place/1286616507</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -760,29 +760,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>24시 코코피트니스 헬스PT필라테스 산남점</t>
+          <t>코코피트니스 헬스 PT 태닝 복대점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>cocogym1@naver.com</t>
+          <t>cocogym_3@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1354-0050</t>
+          <t>0507-1443-0339</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>충북 청주시 서원구 원흥로 17 3층</t>
+          <t>충북 청주시 흥덕구 대농로 43 4층</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/cocogym1</t>
+          <t>https://www.youtube.com/@cocogym3</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -797,7 +797,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -807,7 +807,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4otcd</t>
+          <t>https://talk.naver.com/ct/w4ammk</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -821,13 +821,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>3758</v>
+        <v>3065</v>
       </c>
       <c r="Q4" t="n">
-        <v>2067</v>
+        <v>1814</v>
       </c>
       <c r="R4" t="n">
-        <v>5825</v>
+        <v>4879</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -836,17 +836,17 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1286616507</t>
+          <t>1478272953</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1286616507</t>
+          <t>https://m.place.naver.com/place/1478272953</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -858,29 +858,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>코코피트니스 헬스 PT 태닝 복대점</t>
+          <t>24시 코코피트니스 헬스 PT 율량점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>cocogym_3@naver.com</t>
+          <t>shaminwoo@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1443-0339</t>
+          <t>0507-1377-5496</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>충북 청주시 흥덕구 대농로 43 4층</t>
+          <t>충북 청주시 청원구 율량로190번길 53 비 제4층 제404호</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/@cocogym3</t>
+          <t>https://www.instagram.com/coco_fitxx8</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -905,7 +905,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4ammk</t>
+          <t>https://talk.naver.com/ct/wy2mfy3</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -919,13 +919,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>3064</v>
+        <v>287</v>
       </c>
       <c r="Q5" t="n">
-        <v>1814</v>
+        <v>340</v>
       </c>
       <c r="R5" t="n">
-        <v>4878</v>
+        <v>627</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -934,17 +934,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1478272953</t>
+          <t>2051104888</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1478272953</t>
+          <t>https://m.place.naver.com/place/2051104888</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -956,29 +956,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>24시 코코피트니스 헬스 PT 율량점</t>
+          <t>24시 코코피트니스 헬스PT필라테스 금천점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>shaminwoo@naver.com</t>
+          <t>cocofitness5@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1377-5496</t>
+          <t>0507-1428-5246</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>충북 청주시 청원구 율량로190번길 53 비 제4층 제404호</t>
+          <t>충북 청주시 상당구 중고개로 333 201, 202, 203, 204호</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/coco_fitxx8</t>
+          <t>https://blog.naver.com/cocofitness5</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -993,7 +993,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1003,7 +1003,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wy2mfy3</t>
+          <t>https://talk.naver.com/ct/w4h162</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1017,13 +1017,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>287</v>
+        <v>2668</v>
       </c>
       <c r="Q6" t="n">
-        <v>340</v>
+        <v>1534</v>
       </c>
       <c r="R6" t="n">
-        <v>627</v>
+        <v>4202</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1032,17 +1032,17 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2051104888</t>
+          <t>1016038247</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2051104888</t>
+          <t>https://m.place.naver.com/place/1016038247</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1054,29 +1054,33 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>24시 코코피트니스 헬스PT필라테스 금천점</t>
+          <t>쿠키짐 헬스&amp;PT 오송</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>cocofitness5@naver.com</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>cookiegym@naver.com</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>gotz6170@gmail.com</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1428-5246</t>
+          <t>0507-1371-9224</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>충북 청주시 상당구 중고개로 333 201, 202, 203, 204호</t>
+          <t>충북 청주시 흥덕구 오송읍 오송생명11로 46 608~621호</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/cocofitness5</t>
+          <t>https://youtu.be/UXuiUC4s92M?si=R4exOLNx-6qFB1fg</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1091,7 +1095,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1101,7 +1105,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4h162</t>
+          <t>https://talk.naver.com/ct/w4h6q3</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1115,13 +1119,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>2667</v>
+        <v>3355</v>
       </c>
       <c r="Q7" t="n">
-        <v>1534</v>
+        <v>852</v>
       </c>
       <c r="R7" t="n">
-        <v>4201</v>
+        <v>4207</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1130,55 +1134,51 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1016038247</t>
+          <t>1245970521</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1016038247</t>
+          <t>https://m.place.naver.com/place/1245970521</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>쿠키짐 헬스&amp;PT 오송</t>
+          <t>브로피트니스 금천점 PT헬스</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>cookiegym@naver.com</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>gotz6170@gmail.com</t>
-        </is>
-      </c>
+          <t>brofitness2@naver.com</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1371-9224</t>
+          <t>0507-1342-9698</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>충북 청주시 흥덕구 오송읍 오송생명11로 46 608~621호</t>
+          <t>충북 청주시 상당구 중고개로 307 4층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://youtu.be/UXuiUC4s92M?si=R4exOLNx-6qFB1fg</t>
+          <t>https://blog.naver.com/brofitness2</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1193,7 +1193,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1203,7 +1203,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4h6q3</t>
+          <t>https://talk.naver.com/ct/w4d52a</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1217,13 +1217,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>3355</v>
+        <v>614</v>
       </c>
       <c r="Q8" t="n">
-        <v>850</v>
+        <v>829</v>
       </c>
       <c r="R8" t="n">
-        <v>4205</v>
+        <v>1443</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1232,51 +1232,51 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1245970521</t>
+          <t>1563089367</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1245970521</t>
+          <t>https://m.place.naver.com/place/1563089367</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>브로피트니스 금천점 PT헬스</t>
+          <t>팀온짐 강서점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>brofitness2@naver.com</t>
+          <t>wkddlfwns13@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1342-9698</t>
+          <t>0507-1394-8311</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>충북 청주시 상당구 중고개로 307 4층</t>
+          <t>충북 청주시 흥덕구 가로수로1164번길 41-29 4층 팀온짐</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/brofitness2</t>
+          <t>https://www.instagram.com/team.on.gym_gangseo/</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4d52a</t>
+          <t>https://talk.naver.com/ct/w42g0e</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1315,13 +1315,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>614</v>
+        <v>99</v>
       </c>
       <c r="Q9" t="n">
-        <v>825</v>
+        <v>54</v>
       </c>
       <c r="R9" t="n">
-        <v>1439</v>
+        <v>153</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1330,17 +1330,17 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1563089367</t>
+          <t>1332607968</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1563089367</t>
+          <t>https://m.place.naver.com/place/1332607968</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1438,41 +1438,41 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>필라테스</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>PT라운지 복대점</t>
+          <t>코코필라테스 바레 요가 PT 산남점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>pt_lounge@naver.com</t>
+          <t>cocogym1@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1408-0133</t>
+          <t>0507-1359-4427</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>충북 청주시 흥덕구 대농로 68 MJ트윈스빌딩 601호 PT라운지</t>
+          <t>충북 청주시 서원구 원흥로 17 3층 코코필라테스</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/pt_lounge</t>
+          <t>https://blog.naver.com/cocogym1</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1492,14 +1492,10 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4xfjq</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
           <t>X</t>
@@ -1511,13 +1507,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>449</v>
+        <v>283</v>
       </c>
       <c r="Q11" t="n">
-        <v>955</v>
+        <v>382</v>
       </c>
       <c r="R11" t="n">
-        <v>1404</v>
+        <v>665</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1526,111 +1522,17 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1945520016</t>
+          <t>1421389621</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1945520016</t>
+          <t>https://m.place.naver.com/place/1421389621</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>필라테스</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>코코필라테스 바레 요가 PT 산남점</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>cocogym1@naver.com</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>0507-1359-4427</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>충북 청주시 서원구 원흥로 17 3층 코코필라테스</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>https://blog.naver.com/cocogym1</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P12" t="n">
-        <v>283</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>382</v>
-      </c>
-      <c r="R12" t="n">
-        <v>665</v>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>1421389621</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1421389621</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/청주_헬스장.xlsx
+++ b/naver-place-crawler/results_health/청주_헬스장.xlsx
@@ -417,12 +417,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V11"/>
+  <dimension ref="A1:V12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="25" customWidth="1" min="2" max="2"/>
-    <col width="27" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
@@ -564,29 +564,29 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>휘트니스휴 동남지구점</t>
+          <t>24시 코코피트니스 헬스PT태닝 프리미엄 강서점</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>fithue9679@naver.com</t>
+          <t>grasp1069@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1357-9680</t>
+          <t>0507-1336-5246</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>충북 청주시 상당구 호미로 3 4층</t>
+          <t>충북 청주시 흥덕구 강서로 110 3층</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/fithue9679</t>
+          <t>https://blog.naver.com/grasp1069</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -611,7 +611,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4547b</t>
+          <t>https://talk.naver.com/ct/w4d0wj</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -625,13 +625,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>876</v>
+        <v>4766</v>
       </c>
       <c r="Q2" t="n">
-        <v>618</v>
+        <v>1283</v>
       </c>
       <c r="R2" t="n">
-        <v>1494</v>
+        <v>6049</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -640,12 +640,12 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1870900978</t>
+          <t>1446407109</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1870900978</t>
+          <t>https://m.place.naver.com/place/1446407109</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -662,29 +662,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>24시 코코피트니스 헬스PT필라테스 산남점</t>
+          <t>휘트니스휴 동남지구점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>cocogym1@naver.com</t>
+          <t>fithue9679@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1354-0050</t>
+          <t>0507-1357-9680</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>충북 청주시 서원구 원흥로 17 3층</t>
+          <t>충북 청주시 상당구 호미로 3 4층</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/cocogym1</t>
+          <t>https://blog.naver.com/fithue9679</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -709,7 +709,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4otcd</t>
+          <t>https://talk.naver.com/ct/w4547b</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -723,13 +723,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>3758</v>
+        <v>876</v>
       </c>
       <c r="Q3" t="n">
-        <v>2067</v>
+        <v>618</v>
       </c>
       <c r="R3" t="n">
-        <v>5825</v>
+        <v>1494</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -738,12 +738,12 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1286616507</t>
+          <t>1870900978</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1286616507</t>
+          <t>https://m.place.naver.com/place/1870900978</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -824,10 +824,10 @@
         <v>3065</v>
       </c>
       <c r="Q4" t="n">
-        <v>1814</v>
+        <v>1817</v>
       </c>
       <c r="R4" t="n">
-        <v>4879</v>
+        <v>4882</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -858,29 +858,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>24시 코코피트니스 헬스 PT 율량점</t>
+          <t>24시 코코피트니스 헬스PT필라테스 산남점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>shaminwoo@naver.com</t>
+          <t>cocogym1@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1377-5496</t>
+          <t>0507-1354-0050</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>충북 청주시 청원구 율량로190번길 53 비 제4층 제404호</t>
+          <t>충북 청주시 서원구 원흥로 17 3층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/coco_fitxx8</t>
+          <t>https://blog.naver.com/cocogym1</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -905,7 +905,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wy2mfy3</t>
+          <t>https://talk.naver.com/ct/w4otcd</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -919,13 +919,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>287</v>
+        <v>3758</v>
       </c>
       <c r="Q5" t="n">
-        <v>340</v>
+        <v>2067</v>
       </c>
       <c r="R5" t="n">
-        <v>627</v>
+        <v>5825</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -934,12 +934,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2051104888</t>
+          <t>1286616507</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2051104888</t>
+          <t>https://m.place.naver.com/place/1286616507</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -956,29 +956,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>24시 코코피트니스 헬스PT필라테스 금천점</t>
+          <t>24시 코코피트니스 헬스 PT 율량점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>cocofitness5@naver.com</t>
+          <t>shaminwoo@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1428-5246</t>
+          <t>0507-1377-5496</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>충북 청주시 상당구 중고개로 333 201, 202, 203, 204호</t>
+          <t>충북 청주시 청원구 율량로190번길 53 비 제4층 제404호</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/cocofitness5</t>
+          <t>https://www.instagram.com/coco_fitxx8</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -993,7 +993,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1003,7 +1003,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4h162</t>
+          <t>https://talk.naver.com/ct/wy2mfy3</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1017,13 +1017,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>2668</v>
+        <v>287</v>
       </c>
       <c r="Q6" t="n">
-        <v>1534</v>
+        <v>340</v>
       </c>
       <c r="R6" t="n">
-        <v>4202</v>
+        <v>627</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1032,12 +1032,12 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1016038247</t>
+          <t>2051104888</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1016038247</t>
+          <t>https://m.place.naver.com/place/2051104888</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1054,33 +1054,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>쿠키짐 헬스&amp;PT 오송</t>
+          <t>24시 코코피트니스 헬스PT필라테스 금천점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>cookiegym@naver.com</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>gotz6170@gmail.com</t>
-        </is>
-      </c>
+          <t>cocofitness5@naver.com</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1371-9224</t>
+          <t>0507-1428-5246</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>충북 청주시 흥덕구 오송읍 오송생명11로 46 608~621호</t>
+          <t>충북 청주시 상당구 중고개로 333 201, 202, 203, 204호</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://youtu.be/UXuiUC4s92M?si=R4exOLNx-6qFB1fg</t>
+          <t>https://blog.naver.com/cocofitness5</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1095,7 +1091,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1105,7 +1101,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4h6q3</t>
+          <t>https://talk.naver.com/ct/w4h162</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1119,13 +1115,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>3355</v>
+        <v>2668</v>
       </c>
       <c r="Q7" t="n">
-        <v>852</v>
+        <v>1534</v>
       </c>
       <c r="R7" t="n">
-        <v>4207</v>
+        <v>4202</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1134,12 +1130,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1245970521</t>
+          <t>1016038247</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1245970521</t>
+          <t>https://m.place.naver.com/place/1016038247</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1151,34 +1147,38 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>브로피트니스 금천점 PT헬스</t>
+          <t>쿠키짐 헬스&amp;PT 오송</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>brofitness2@naver.com</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>cookiegym@naver.com</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>gotz6170@gmail.com</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1342-9698</t>
+          <t>0507-1371-9224</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>충북 청주시 상당구 중고개로 307 4층</t>
+          <t>충북 청주시 흥덕구 오송읍 오송생명11로 46 608~621호</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/brofitness2</t>
+          <t>https://youtu.be/UXuiUC4s92M?si=R4exOLNx-6qFB1fg</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1193,7 +1193,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1203,7 +1203,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4d52a</t>
+          <t>https://talk.naver.com/ct/w4h6q3</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1217,13 +1217,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>614</v>
+        <v>3355</v>
       </c>
       <c r="Q8" t="n">
-        <v>829</v>
+        <v>852</v>
       </c>
       <c r="R8" t="n">
-        <v>1443</v>
+        <v>4207</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1232,12 +1232,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1563089367</t>
+          <t>1245970521</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1563089367</t>
+          <t>https://m.place.naver.com/place/1245970521</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1249,34 +1249,34 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>팀온짐 강서점</t>
+          <t>브로피트니스 금천점 PT헬스</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>wkddlfwns13@naver.com</t>
+          <t>brofitness2@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1394-8311</t>
+          <t>0507-1342-9698</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>충북 청주시 흥덕구 가로수로1164번길 41-29 4층 팀온짐</t>
+          <t>충북 청주시 상당구 중고개로 307 4층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/team.on.gym_gangseo/</t>
+          <t>https://blog.naver.com/brofitness2</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w42g0e</t>
+          <t>https://talk.naver.com/ct/w4d52a</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1315,13 +1315,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>99</v>
+        <v>614</v>
       </c>
       <c r="Q9" t="n">
-        <v>54</v>
+        <v>829</v>
       </c>
       <c r="R9" t="n">
-        <v>153</v>
+        <v>1443</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1330,12 +1330,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1332607968</t>
+          <t>1563089367</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1332607968</t>
+          <t>https://m.place.naver.com/place/1563089367</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1352,29 +1352,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>오창헬스장 바디플러스휘트니스</t>
+          <t>팀온짐 강서점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>bodyplusfitness@naver.com</t>
+          <t>wkddlfwns13@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1338-2081</t>
+          <t>0507-1394-8311</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>충북 청주시 청원구 오창읍 오창중앙로 123-8 메디하우스 6층</t>
+          <t>충북 청주시 흥덕구 가로수로1164번길 41-29 4층 팀온짐</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/bodyplusfitness</t>
+          <t>https://www.instagram.com/team.on.gym_gangseo/</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1389,7 +1389,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1399,7 +1399,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4ptuz</t>
+          <t>https://talk.naver.com/ct/w42g0e</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1413,13 +1413,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>297</v>
+        <v>99</v>
       </c>
       <c r="Q10" t="n">
-        <v>407</v>
+        <v>54</v>
       </c>
       <c r="R10" t="n">
-        <v>704</v>
+        <v>153</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1428,12 +1428,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1682187425</t>
+          <t>1332607968</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1682187425</t>
+          <t>https://m.place.naver.com/place/1332607968</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1445,92 +1445,190 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>필라테스</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>코코필라테스 바레 요가 PT 산남점</t>
+          <t>네오바디짐 율량점 헬스 PT</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>cocogym1@naver.com</t>
+          <t>neobodygym@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1359-4427</t>
+          <t>0507-1314-5116</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
+          <t>충북 청주시 청원구 사뜸로 70 상가동 지하1층</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/neobodygym</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wy4h5jc</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P11" t="n">
+        <v>120</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>63</v>
+      </c>
+      <c r="R11" t="n">
+        <v>183</v>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>2045981331</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2045981331</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>필라테스</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>코코필라테스 바레 요가 PT 산남점</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>cocogym1@naver.com</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0507-1359-4427</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
           <t>충북 청주시 서원구 원흥로 17 3층 코코필라테스</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>https://blog.naver.com/cocogym1</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P11" t="n">
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
         <v>283</v>
       </c>
-      <c r="Q11" t="n">
+      <c r="Q12" t="n">
         <v>382</v>
       </c>
-      <c r="R11" t="n">
+      <c r="R12" t="n">
         <v>665</v>
       </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
         <is>
           <t>1421389621</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="U12" t="inlineStr">
         <is>
           <t>https://m.place.naver.com/place/1421389621</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="V12" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>

--- a/naver-place-crawler/results_health/청주_헬스장.xlsx
+++ b/naver-place-crawler/results_health/청주_헬스장.xlsx
@@ -422,11 +422,11 @@
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="27" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="41" customWidth="1" min="7" max="7"/>
+    <col width="37" customWidth="1" min="7" max="7"/>
     <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
@@ -625,13 +625,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>4766</v>
+        <v>4767</v>
       </c>
       <c r="Q2" t="n">
-        <v>1283</v>
+        <v>1284</v>
       </c>
       <c r="R2" t="n">
-        <v>6049</v>
+        <v>6051</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -760,29 +760,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>코코피트니스 헬스 PT 태닝 복대점</t>
+          <t>24시 코코피트니스 헬스PT필라테스 산남점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>cocogym_3@naver.com</t>
+          <t>cocogym1@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1443-0339</t>
+          <t>0507-1354-0050</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>충북 청주시 흥덕구 대농로 43 4층</t>
+          <t>충북 청주시 서원구 원흥로 17 3층</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/@cocogym3</t>
+          <t>https://blog.naver.com/cocogym1</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -797,7 +797,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -807,7 +807,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4ammk</t>
+          <t>https://talk.naver.com/ct/w4otcd</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -821,13 +821,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>3065</v>
+        <v>3758</v>
       </c>
       <c r="Q4" t="n">
-        <v>1817</v>
+        <v>2068</v>
       </c>
       <c r="R4" t="n">
-        <v>4882</v>
+        <v>5826</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -836,12 +836,12 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1478272953</t>
+          <t>1286616507</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1478272953</t>
+          <t>https://m.place.naver.com/place/1286616507</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -858,29 +858,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>24시 코코피트니스 헬스PT필라테스 산남점</t>
+          <t>코코피트니스 헬스 PT 태닝 복대점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>cocogym1@naver.com</t>
+          <t>cocogym_3@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1354-0050</t>
+          <t>0507-1443-0339</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>충북 청주시 서원구 원흥로 17 3층</t>
+          <t>충청북도 청주시 흥덕구 대농로 43 4층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/cocogym1</t>
+          <t>https://www.youtube.com/@cocogym3</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -895,19 +895,15 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4otcd</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
           <t>X</t>
@@ -919,13 +915,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>3758</v>
+        <v>3065</v>
       </c>
       <c r="Q5" t="n">
-        <v>2067</v>
+        <v>1819</v>
       </c>
       <c r="R5" t="n">
-        <v>5825</v>
+        <v>4884</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -934,12 +930,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1286616507</t>
+          <t>1478272953</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1286616507</t>
+          <t>https://m.place.naver.com/place/1478272953</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1017,13 +1013,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q6" t="n">
         <v>340</v>
       </c>
       <c r="R6" t="n">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1049,34 +1045,34 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>24시 코코피트니스 헬스PT필라테스 금천점</t>
+          <t>브로피트니스 금천점 PT헬스</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>cocofitness5@naver.com</t>
+          <t>brofitness2@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1428-5246</t>
+          <t>0507-1342-9698</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>충북 청주시 상당구 중고개로 333 201, 202, 203, 204호</t>
+          <t>충북 청주시 상당구 중고개로 307 4층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/cocofitness5</t>
+          <t>https://blog.naver.com/brofitness2</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1101,7 +1097,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4h162</t>
+          <t>https://talk.naver.com/ct/w4d52a</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1115,13 +1111,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>2668</v>
+        <v>615</v>
       </c>
       <c r="Q7" t="n">
-        <v>1534</v>
+        <v>829</v>
       </c>
       <c r="R7" t="n">
-        <v>4202</v>
+        <v>1444</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1130,12 +1126,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1016038247</t>
+          <t>1563089367</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1016038247</t>
+          <t>https://m.place.naver.com/place/1563089367</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1249,34 +1245,34 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>브로피트니스 금천점 PT헬스</t>
+          <t>네오바디짐 율량점 헬스 PT</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>brofitness2@naver.com</t>
+          <t>neobodygym@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1342-9698</t>
+          <t>0507-1314-5116</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>충북 청주시 상당구 중고개로 307 4층</t>
+          <t>충북 청주시 청원구 사뜸로 70 상가동 지하1층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/brofitness2</t>
+          <t>https://blog.naver.com/neobodygym</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1301,7 +1297,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4d52a</t>
+          <t>https://talk.naver.com/ct/wy4h5jc</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1315,13 +1311,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>614</v>
+        <v>121</v>
       </c>
       <c r="Q9" t="n">
-        <v>829</v>
+        <v>63</v>
       </c>
       <c r="R9" t="n">
-        <v>1443</v>
+        <v>184</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1330,12 +1326,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1563089367</t>
+          <t>2045981331</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1563089367</t>
+          <t>https://m.place.naver.com/place/2045981331</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1352,29 +1348,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>팀온짐 강서점</t>
+          <t>오창헬스장 바디플러스휘트니스</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>wkddlfwns13@naver.com</t>
+          <t>bodyplusfitness@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1394-8311</t>
+          <t>0507-1338-2081</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>충북 청주시 흥덕구 가로수로1164번길 41-29 4층 팀온짐</t>
+          <t>충북 청주시 청원구 오창읍 오창중앙로 123-8 메디하우스 6층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/team.on.gym_gangseo/</t>
+          <t>https://blog.naver.com/bodyplusfitness</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1389,7 +1385,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1399,7 +1395,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w42g0e</t>
+          <t>https://talk.naver.com/ct/w4ptuz</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1413,13 +1409,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>99</v>
+        <v>297</v>
       </c>
       <c r="Q10" t="n">
-        <v>54</v>
+        <v>407</v>
       </c>
       <c r="R10" t="n">
-        <v>153</v>
+        <v>704</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1428,12 +1424,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1332607968</t>
+          <t>1682187425</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1332607968</t>
+          <t>https://m.place.naver.com/place/1682187425</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1450,29 +1446,29 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>네오바디짐 율량점 헬스 PT</t>
+          <t>고트짐</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>neobodygym@naver.com</t>
+          <t>goatgym@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1314-5116</t>
+          <t>0507-1465-1987</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>충북 청주시 청원구 사뜸로 70 상가동 지하1층</t>
+          <t>충북 청주시 흥덕구 죽천로 141 세종청수빌딩 F층</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/neobodygym</t>
+          <t>https://blog.naver.com/goatgym</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1497,7 +1493,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wy4h5jc</t>
+          <t>https://talk.naver.com/ct/w5vonm</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1511,13 +1507,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>120</v>
+        <v>64</v>
       </c>
       <c r="Q11" t="n">
-        <v>63</v>
+        <v>38</v>
       </c>
       <c r="R11" t="n">
-        <v>183</v>
+        <v>102</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1526,12 +1522,12 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2045981331</t>
+          <t>1290455974</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2045981331</t>
+          <t>https://m.place.naver.com/place/1290455974</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -1543,34 +1539,34 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>필라테스</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>코코필라테스 바레 요가 PT 산남점</t>
+          <t>빅스짐 청주고속터미널점</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>cocogym1@naver.com</t>
+          <t>bigsgymgagyeong@naver.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0507-1359-4427</t>
+          <t>0507-1364-8896</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>충북 청주시 서원구 원흥로 17 3층 코코필라테스</t>
+          <t>충북 청주시 흥덕구 강서로 118 장한빌딩 6층 601-605호</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/cocogym1</t>
+          <t>https://www.instagram.com/bigsgym_cheongju/</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1585,15 +1581,19 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w456me</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr">
         <is>
           <t>X</t>
@@ -1605,13 +1605,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>283</v>
+        <v>5310</v>
       </c>
       <c r="Q12" t="n">
-        <v>382</v>
+        <v>1293</v>
       </c>
       <c r="R12" t="n">
-        <v>665</v>
+        <v>6603</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1620,12 +1620,12 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>1421389621</t>
+          <t>1689856448</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1421389621</t>
+          <t>https://m.place.naver.com/place/1689856448</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">

--- a/naver-place-crawler/results_health/청주_헬스장.xlsx
+++ b/naver-place-crawler/results_health/청주_헬스장.xlsx
@@ -417,12 +417,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V12"/>
+  <dimension ref="A1:V11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="27" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
@@ -628,10 +628,10 @@
         <v>4767</v>
       </c>
       <c r="Q2" t="n">
-        <v>1284</v>
+        <v>1286</v>
       </c>
       <c r="R2" t="n">
-        <v>6051</v>
+        <v>6053</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -650,7 +650,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -824,10 +824,10 @@
         <v>3758</v>
       </c>
       <c r="Q4" t="n">
-        <v>2068</v>
+        <v>2070</v>
       </c>
       <c r="R4" t="n">
-        <v>5826</v>
+        <v>5828</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -846,7 +846,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -875,7 +875,7 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>충청북도 청주시 흥덕구 대농로 43 4층</t>
+          <t>충북 청주시 흥덕구 대농로 43 4층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -900,10 +900,14 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4ammk</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr">
         <is>
           <t>X</t>
@@ -915,13 +919,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>3065</v>
+        <v>3066</v>
       </c>
       <c r="Q5" t="n">
         <v>1819</v>
       </c>
       <c r="R5" t="n">
-        <v>4884</v>
+        <v>4885</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -940,7 +944,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1013,13 +1017,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q6" t="n">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="R6" t="n">
-        <v>628</v>
+        <v>631</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1038,7 +1042,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1136,7 +1140,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1238,7 +1242,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1250,29 +1254,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>네오바디짐 율량점 헬스 PT</t>
+          <t>오창헬스장 바디플러스휘트니스</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>neobodygym@naver.com</t>
+          <t>bodyplusfitness@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1314-5116</t>
+          <t>0507-1338-2081</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>충북 청주시 청원구 사뜸로 70 상가동 지하1층</t>
+          <t>충북 청주시 청원구 오창읍 오창중앙로 123-8 메디하우스 6층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/neobodygym</t>
+          <t>https://blog.naver.com/bodyplusfitness</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1297,7 +1301,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wy4h5jc</t>
+          <t>https://talk.naver.com/ct/w4ptuz</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1311,13 +1315,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>121</v>
+        <v>297</v>
       </c>
       <c r="Q9" t="n">
-        <v>63</v>
+        <v>407</v>
       </c>
       <c r="R9" t="n">
-        <v>184</v>
+        <v>704</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1326,17 +1330,17 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2045981331</t>
+          <t>1682187425</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2045981331</t>
+          <t>https://m.place.naver.com/place/1682187425</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1348,29 +1352,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>오창헬스장 바디플러스휘트니스</t>
+          <t>쌍둥이휘트니스</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>bodyplusfitness@naver.com</t>
+          <t>ssangdoonge00072@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1338-2081</t>
+          <t>0507-1380-4951</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>충북 청주시 청원구 오창읍 오창중앙로 123-8 메디하우스 6층</t>
+          <t>충북 청주시 흥덕구 1순환로 606 바이크짱 2층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/bodyplusfitness</t>
+          <t>https://www.instagram.com/ssangdungi_fitness/</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1385,7 +1389,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1395,7 +1399,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4ptuz</t>
+          <t>https://talk.naver.com/ct/w41si2</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1409,13 +1413,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>297</v>
+        <v>162</v>
       </c>
       <c r="Q10" t="n">
-        <v>407</v>
+        <v>16</v>
       </c>
       <c r="R10" t="n">
-        <v>704</v>
+        <v>178</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1424,51 +1428,51 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1682187425</t>
+          <t>37435004</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1682187425</t>
+          <t>https://m.place.naver.com/place/37435004</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>고트짐</t>
+          <t>빅스짐 청주고속터미널점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>goatgym@naver.com</t>
+          <t>bigsgymgagyeong@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1465-1987</t>
+          <t>0507-1364-8896</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>충북 청주시 흥덕구 죽천로 141 세종청수빌딩 F층</t>
+          <t>충북 청주시 흥덕구 강서로 118 장한빌딩 6층 601-605호</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/goatgym</t>
+          <t>https://www.instagram.com/bigsgym_cheongju/</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1483,7 +1487,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1493,7 +1497,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5vonm</t>
+          <t>https://talk.naver.com/ct/w456me</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1507,13 +1511,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>64</v>
+        <v>5311</v>
       </c>
       <c r="Q11" t="n">
-        <v>38</v>
+        <v>1293</v>
       </c>
       <c r="R11" t="n">
-        <v>102</v>
+        <v>6604</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1522,115 +1526,17 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1290455974</t>
+          <t>1689856448</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1290455974</t>
+          <t>https://m.place.naver.com/place/1689856448</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>스포츠시설</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>빅스짐 청주고속터미널점</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>bigsgymgagyeong@naver.com</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>0507-1364-8896</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>충북 청주시 흥덕구 강서로 118 장한빌딩 6층 601-605호</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/bigsgym_cheongju/</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w456me</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P12" t="n">
-        <v>5310</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>1293</v>
-      </c>
-      <c r="R12" t="n">
-        <v>6603</v>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>1689856448</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1689856448</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/청주_헬스장.xlsx
+++ b/naver-place-crawler/results_health/청주_헬스장.xlsx
@@ -417,12 +417,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V11"/>
+  <dimension ref="A1:V12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="27" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
@@ -628,10 +628,10 @@
         <v>4767</v>
       </c>
       <c r="Q2" t="n">
-        <v>1286</v>
+        <v>1290</v>
       </c>
       <c r="R2" t="n">
-        <v>6053</v>
+        <v>6057</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -723,13 +723,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="Q3" t="n">
         <v>618</v>
       </c>
       <c r="R3" t="n">
-        <v>1494</v>
+        <v>1495</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -824,10 +824,10 @@
         <v>3758</v>
       </c>
       <c r="Q4" t="n">
-        <v>2070</v>
+        <v>2073</v>
       </c>
       <c r="R4" t="n">
-        <v>5828</v>
+        <v>5831</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -885,7 +885,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -922,10 +922,10 @@
         <v>3066</v>
       </c>
       <c r="Q5" t="n">
-        <v>1819</v>
+        <v>1822</v>
       </c>
       <c r="R5" t="n">
-        <v>4885</v>
+        <v>4888</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -1017,13 +1017,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q6" t="n">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="R6" t="n">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1118,10 +1118,10 @@
         <v>615</v>
       </c>
       <c r="Q7" t="n">
-        <v>829</v>
+        <v>835</v>
       </c>
       <c r="R7" t="n">
-        <v>1444</v>
+        <v>1450</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1152,33 +1152,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>쿠키짐 헬스&amp;PT 오송</t>
+          <t>나우휘트니스</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>cookiegym@naver.com</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>gotz6170@gmail.com</t>
-        </is>
-      </c>
+          <t>rlatjs031@naver.com</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1371-9224</t>
+          <t>0507-1411-7778</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>충북 청주시 흥덕구 오송읍 오송생명11로 46 608~621호</t>
+          <t>충북 청주시 서원구 예체로 23 상원빌딩 2,3층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://youtu.be/UXuiUC4s92M?si=R4exOLNx-6qFB1fg</t>
+          <t>https://blog.naver.com/rlatjs031/224067153765</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1193,7 +1189,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1203,7 +1199,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4h6q3</t>
+          <t>https://talk.naver.com/ct/wc439z</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1217,13 +1213,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>3355</v>
+        <v>1686</v>
       </c>
       <c r="Q8" t="n">
-        <v>852</v>
+        <v>5607</v>
       </c>
       <c r="R8" t="n">
-        <v>4207</v>
+        <v>7293</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1232,12 +1228,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1245970521</t>
+          <t>33237461</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1245970521</t>
+          <t>https://m.place.naver.com/place/33237461</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1254,34 +1250,38 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>오창헬스장 바디플러스휘트니스</t>
+          <t>쿠키짐 헬스&amp;PT 오송</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>bodyplusfitness@naver.com</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>cookiegym@naver.com</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>gotz6170@gmail.com</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1338-2081</t>
+          <t>0507-1371-9224</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>충북 청주시 청원구 오창읍 오창중앙로 123-8 메디하우스 6층</t>
+          <t>충북 청주시 흥덕구 오송읍 오송생명11로 46 608~621호</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/bodyplusfitness</t>
+          <t>https://youtu.be/UXuiUC4s92M?si=R4exOLNx-6qFB1fg</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4ptuz</t>
+          <t>https://talk.naver.com/ct/w4h6q3</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1315,13 +1315,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>297</v>
+        <v>3354</v>
       </c>
       <c r="Q9" t="n">
-        <v>407</v>
+        <v>852</v>
       </c>
       <c r="R9" t="n">
-        <v>704</v>
+        <v>4206</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1330,12 +1330,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1682187425</t>
+          <t>1245970521</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1682187425</t>
+          <t>https://m.place.naver.com/place/1245970521</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1352,29 +1352,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>쌍둥이휘트니스</t>
+          <t>오창헬스장 바디플러스휘트니스</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>ssangdoonge00072@naver.com</t>
+          <t>bodyplusfitness@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1380-4951</t>
+          <t>0507-1338-2081</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>충북 청주시 흥덕구 1순환로 606 바이크짱 2층</t>
+          <t>충북 청주시 청원구 오창읍 오창중앙로 123-8 메디하우스 6층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/ssangdungi_fitness/</t>
+          <t>https://blog.naver.com/bodyplusfitness</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1389,7 +1389,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1399,7 +1399,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w41si2</t>
+          <t>https://talk.naver.com/ct/w4ptuz</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1413,13 +1413,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>162</v>
+        <v>297</v>
       </c>
       <c r="Q10" t="n">
-        <v>16</v>
+        <v>407</v>
       </c>
       <c r="R10" t="n">
-        <v>178</v>
+        <v>704</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1428,12 +1428,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>37435004</t>
+          <t>1682187425</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37435004</t>
+          <t>https://m.place.naver.com/place/1682187425</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1445,96 +1445,194 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>빅스짐 청주고속터미널점</t>
+          <t>고트짐</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>bigsgymgagyeong@naver.com</t>
+          <t>goatgym@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1364-8896</t>
+          <t>0507-1465-1987</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
+          <t>충북 청주시 흥덕구 죽천로 141 세종청수빌딩 F층</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/goatgym</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5vonm</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P11" t="n">
+        <v>64</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>38</v>
+      </c>
+      <c r="R11" t="n">
+        <v>102</v>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>1290455974</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1290455974</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>빅스짐 청주고속터미널점</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>bigsgymgagyeong@naver.com</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0507-1364-8896</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
           <t>충북 청주시 흥덕구 강서로 118 장한빌딩 6층 601-605호</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>https://www.instagram.com/bigsgym_cheongju/</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
         <is>
           <t>https://talk.naver.com/ct/w456me</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P11" t="n">
-        <v>5311</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>1293</v>
-      </c>
-      <c r="R11" t="n">
-        <v>6604</v>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>5312</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1294</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6606</v>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
         <is>
           <t>1689856448</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="U12" t="inlineStr">
         <is>
           <t>https://m.place.naver.com/place/1689856448</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="V12" t="inlineStr">
         <is>
           <t>2026-04-28</t>
         </is>

--- a/naver-place-crawler/results_health/청주_헬스장.xlsx
+++ b/naver-place-crawler/results_health/청주_헬스장.xlsx
@@ -625,13 +625,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>4767</v>
+        <v>4769</v>
       </c>
       <c r="Q2" t="n">
         <v>1290</v>
       </c>
       <c r="R2" t="n">
-        <v>6057</v>
+        <v>6059</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -650,7 +650,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1017,13 +1017,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q6" t="n">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="R6" t="n">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1115,13 +1115,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="Q7" t="n">
         <v>835</v>
       </c>
       <c r="R7" t="n">
-        <v>1450</v>
+        <v>1451</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1213,13 +1213,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1686</v>
+        <v>1689</v>
       </c>
       <c r="Q8" t="n">
-        <v>5607</v>
+        <v>5609</v>
       </c>
       <c r="R8" t="n">
-        <v>7293</v>
+        <v>7298</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1250,38 +1250,34 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>쿠키짐 헬스&amp;PT 오송</t>
+          <t>팀온짐 강서점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>cookiegym@naver.com</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>gotz6170@gmail.com</t>
-        </is>
-      </c>
+          <t>wkddlfwns13@naver.com</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1371-9224</t>
+          <t>0507-1394-8311</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>충북 청주시 흥덕구 오송읍 오송생명11로 46 608~621호</t>
+          <t>충북 청주시 흥덕구 가로수로1164번길 41-29 4층 팀온짐</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://youtu.be/UXuiUC4s92M?si=R4exOLNx-6qFB1fg</t>
+          <t>https://www.instagram.com/team.on.gym_gangseo/</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1301,7 +1297,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4h6q3</t>
+          <t>https://talk.naver.com/ct/w42g0e</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1315,13 +1311,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>3354</v>
+        <v>99</v>
       </c>
       <c r="Q9" t="n">
-        <v>852</v>
+        <v>57</v>
       </c>
       <c r="R9" t="n">
-        <v>4206</v>
+        <v>156</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1330,17 +1326,17 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1245970521</t>
+          <t>1332607968</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1245970521</t>
+          <t>https://m.place.naver.com/place/1332607968</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1352,34 +1348,38 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>오창헬스장 바디플러스휘트니스</t>
+          <t>쿠키짐 헬스&amp;PT 오송</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>bodyplusfitness@naver.com</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>cookiegym@naver.com</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>gotz6170@gmail.com</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1338-2081</t>
+          <t>0507-1371-9224</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>충북 청주시 청원구 오창읍 오창중앙로 123-8 메디하우스 6층</t>
+          <t>충북 청주시 흥덕구 오송읍 오송생명11로 46 608~621호</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/bodyplusfitness</t>
+          <t>https://youtu.be/UXuiUC4s92M?si=R4exOLNx-6qFB1fg</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1389,7 +1389,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1399,7 +1399,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4ptuz</t>
+          <t>https://talk.naver.com/ct/w4h6q3</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1413,13 +1413,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>297</v>
+        <v>3354</v>
       </c>
       <c r="Q10" t="n">
-        <v>407</v>
+        <v>855</v>
       </c>
       <c r="R10" t="n">
-        <v>704</v>
+        <v>4209</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1428,17 +1428,17 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1682187425</t>
+          <t>1245970521</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1682187425</t>
+          <t>https://m.place.naver.com/place/1245970521</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1450,29 +1450,29 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>고트짐</t>
+          <t>오창헬스장 바디플러스휘트니스</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>goatgym@naver.com</t>
+          <t>bodyplusfitness@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1465-1987</t>
+          <t>0507-1338-2081</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>충북 청주시 흥덕구 죽천로 141 세종청수빌딩 F층</t>
+          <t>충북 청주시 청원구 오창읍 오창중앙로 123-8 메디하우스 6층</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/goatgym</t>
+          <t>https://blog.naver.com/bodyplusfitness</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1497,7 +1497,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5vonm</t>
+          <t>https://talk.naver.com/ct/w4ptuz</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1511,13 +1511,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>64</v>
+        <v>297</v>
       </c>
       <c r="Q11" t="n">
-        <v>38</v>
+        <v>407</v>
       </c>
       <c r="R11" t="n">
-        <v>102</v>
+        <v>704</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1526,17 +1526,17 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1290455974</t>
+          <t>1682187425</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1290455974</t>
+          <t>https://m.place.naver.com/place/1682187425</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1609,13 +1609,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>5312</v>
+        <v>5314</v>
       </c>
       <c r="Q12" t="n">
         <v>1294</v>
       </c>
       <c r="R12" t="n">
-        <v>6606</v>
+        <v>6608</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1634,7 +1634,7 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/청주_헬스장.xlsx
+++ b/naver-place-crawler/results_health/청주_헬스장.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V12"/>
+  <dimension ref="A1:V11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1445,34 +1445,34 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>오창헬스장 바디플러스휘트니스</t>
+          <t>빅스짐 청주고속터미널점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>bodyplusfitness@naver.com</t>
+          <t>bigsgymgagyeong@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1338-2081</t>
+          <t>0507-1364-8896</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>충북 청주시 청원구 오창읍 오창중앙로 123-8 메디하우스 6층</t>
+          <t>충북 청주시 흥덕구 강서로 118 장한빌딩 6층 601-605호</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/bodyplusfitness</t>
+          <t>https://www.instagram.com/bigsgym_cheongju/</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1487,7 +1487,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1497,7 +1497,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4ptuz</t>
+          <t>https://talk.naver.com/ct/w456me</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1511,13 +1511,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>297</v>
+        <v>5314</v>
       </c>
       <c r="Q11" t="n">
-        <v>407</v>
+        <v>1294</v>
       </c>
       <c r="R11" t="n">
-        <v>704</v>
+        <v>6608</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1526,113 +1526,15 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1682187425</t>
+          <t>1689856448</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1682187425</t>
+          <t>https://m.place.naver.com/place/1689856448</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>스포츠시설</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>빅스짐 청주고속터미널점</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>bigsgymgagyeong@naver.com</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>0507-1364-8896</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>충북 청주시 흥덕구 강서로 118 장한빌딩 6층 601-605호</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/bigsgym_cheongju/</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w456me</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P12" t="n">
-        <v>5314</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>1294</v>
-      </c>
-      <c r="R12" t="n">
-        <v>6608</v>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>1689856448</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1689856448</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
         <is>
           <t>2026-04-29</t>
         </is>
